--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576356566</v>
+        <v>46157.93121523319</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121523319</v>
+        <v>46157.9318719262</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318719262</v>
+        <v>46157.93407945124</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407945124</v>
+        <v>46157.93725774384</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725774384</v>
+        <v>46158.2822326336</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822326336</v>
+        <v>46158.29713651684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713651684</v>
+        <v>46158.29823522113</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823522113</v>
+        <v>46158.33394328372</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394328372</v>
+        <v>46158.36864080268</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Козленко- соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864080268</v>
+        <v>46158.37295064169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
